--- a/E911 Workbook.xlsx
+++ b/E911 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\My Documents\Jobs\C1\C1_Docs\E911\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB8D1D1-6F24-4874-B158-7031DF3A6E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EAB6BB-E07F-48A5-A197-D54020C351AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{57AF9C9E-AD33-4CD7-B4AB-20707E2E81EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{57AF9C9E-AD33-4CD7-B4AB-20707E2E81EE}"/>
   </bookViews>
   <sheets>
     <sheet name="CivicAddress" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="98">
   <si>
     <t>Description</t>
   </si>
@@ -124,9 +124,6 @@
     <t>112.0.0.0</t>
   </si>
   <si>
-    <t>LocationID (Generated from This Process)</t>
-  </si>
-  <si>
     <t>PostDirection</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
   </si>
   <si>
     <t>LocationName</t>
-  </si>
-  <si>
-    <t>NetTopoCommand</t>
   </si>
   <si>
     <t>OH1</t>
@@ -324,6 +318,24 @@
   <si>
     <t>CivicAddressDefaultLocID (Leave Blank)</t>
   </si>
+  <si>
+    <t>LocationID (Generated in this process)</t>
+  </si>
+  <si>
+    <t>Emergency Calling Policy Creation Command</t>
+  </si>
+  <si>
+    <t>Network Topology Site Creation Command</t>
+  </si>
+  <si>
+    <t>Emergency Address Site Creation Command</t>
+  </si>
+  <si>
+    <t>Emergency Address Subnet Add Comand</t>
+  </si>
+  <si>
+    <t>Network Topology Subnet Add Command</t>
+  </si>
 </sst>
 </file>
 
@@ -416,13 +428,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7F82F32-60F5-4DD0-9124-05B390AE4408}" name="Table1" displayName="Table1" ref="A1:Q96" totalsRowShown="0">
-  <autoFilter ref="A1:Q96" xr:uid="{C7F82F32-60F5-4DD0-9124-05B390AE4408}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7F82F32-60F5-4DD0-9124-05B390AE4408}" name="Table1" displayName="Table1" ref="A1:S96" totalsRowShown="0">
+  <autoFilter ref="A1:S96" xr:uid="{C7F82F32-60F5-4DD0-9124-05B390AE4408}">
     <filterColumn colId="0">
       <filters blank="1"/>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="17">
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{52067901-63D5-43B5-A557-55EFEDF0AB45}" name="CivicAddressName"/>
     <tableColumn id="17" xr3:uid="{DB13E8F3-372F-4846-A4B6-39174BB3C706}" name="CivicAddressID (Leave Blank)"/>
     <tableColumn id="16" xr3:uid="{208D8847-2992-49B5-834B-CD2A268FA7C1}" name="CivicAddressDefaultLocID (Leave Blank)"/>
@@ -439,7 +451,9 @@
     <tableColumn id="12" xr3:uid="{233F902C-72EA-4528-9B2E-01409450E652}" name="ELIN_TAG - Optional"/>
     <tableColumn id="13" xr3:uid="{B125621E-0585-4A2B-86EE-54E7EF9A8899}" name="Latitude"/>
     <tableColumn id="14" xr3:uid="{CB2A8EFD-9A23-4C9B-A149-7AAFDB905679}" name="Longitude"/>
-    <tableColumn id="15" xr3:uid="{0DE96BEF-11EA-4242-94EF-D5217C8F51DB}" name="Command"/>
+    <tableColumn id="15" xr3:uid="{0DE96BEF-11EA-4242-94EF-D5217C8F51DB}" name="Emergency Address Site Creation Command"/>
+    <tableColumn id="20" xr3:uid="{58EE357A-F0BD-4730-8F6B-629FCDB4A88F}" name="Emergency Calling Policy Creation Command"/>
+    <tableColumn id="18" xr3:uid="{80EB7475-9ACD-4F2A-BF73-AC0AE416B3A6}" name="Network Topology Site Creation Command"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -453,7 +467,7 @@
     <tableColumn id="6" xr3:uid="{DAF10671-6023-45B9-8FDA-6363004347B7}" name="CivicAddressID (Leave Blank)"/>
     <tableColumn id="2" xr3:uid="{2CBDFA94-8523-4029-B1FC-EF48C8A05471}" name="CivicAddressLocId (Leave Blank)" dataCellStyle="Normal"/>
     <tableColumn id="3" xr3:uid="{02D4B160-36A1-4756-98EC-A079F7CD1F33}" name="LocationName (Description)" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{312F46C9-DE96-493C-A221-4FADEE17B941}" name="LocationID (Generated from This Process)" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{312F46C9-DE96-493C-A221-4FADEE17B941}" name="LocationID (Generated in this process)" dataCellStyle="Normal"/>
     <tableColumn id="4" xr3:uid="{78658000-6A22-4B94-9137-32726F7E3F81}" name="Command" dataCellStyle="Normal">
       <calculatedColumnFormula>CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B2,"' -Location '",D2,"'")</calculatedColumnFormula>
     </tableColumn>
@@ -523,10 +537,10 @@
     <tableColumn id="3" xr3:uid="{C8333E8C-118E-4D30-8A03-50E9C7BDCF1B}" name="LocationName"/>
     <tableColumn id="4" xr3:uid="{27F2A727-2744-491E-997F-71C727FBB49B}" name="CivicAddressName"/>
     <tableColumn id="6" xr3:uid="{C6872729-2DE2-4119-A044-3F1F33909F27}" name="LocationId (Leave Blank)"/>
-    <tableColumn id="5" xr3:uid="{516CD4A5-A9BF-4A04-AB18-BF95E2499260}" name="Command">
+    <tableColumn id="5" xr3:uid="{516CD4A5-A9BF-4A04-AB18-BF95E2499260}" name="Emergency Address Subnet Add Comand">
       <calculatedColumnFormula>CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A2,"' -LocationID '",F2,"' -Description '",C2,"'")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{65248A3B-8923-4330-AB11-BBC3AF23D88B}" name="NetTopoCommand">
+    <tableColumn id="8" xr3:uid="{65248A3B-8923-4330-AB11-BBC3AF23D88B}" name="Network Topology Subnet Add Command">
       <calculatedColumnFormula>CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A2,"' -MaskBits '",B2,"' -Description '",C2,"' -NetworkSiteID '",E2,"'")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -869,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88468DA2-8C59-4761-AE2B-1B01B421C261}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -887,18 +901,20 @@
     <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
     <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="224" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="85.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="94.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -910,7 +926,7 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
@@ -919,7 +935,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K1" t="s">
         <v>4</v>
@@ -931,7 +947,7 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O1" t="s">
         <v>7</v>
@@ -940,12 +956,18 @@
         <v>8</v>
       </c>
       <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="R1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -979,13 +1001,21 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="str">
-        <f t="shared" ref="Q2:Q4" si="0">CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A2,"' -CompanyName '",  D2,"' -CountryOrRegion '",  E2,"' -HouseNumber '",  F2,"' -PreDirectional '",  G2, "' -StreetName '",  H2,"' -StreetSuffix '",  I2,"' -City '",  K2,"' -StateOrProvince '",  L2,"' -PostalCode '",  M2,"' -Latitude '",  O2,"' -Longitude '",  P2,"'")</f>
-        <v>New-CsOnlineLisCivicAddress -Description 'OH1' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '100' -PreDirectional '' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'OH' -PostalCode '44314' -Latitude '' -Longitude ''</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f>CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A2,"' -CompanyName '",  D2,"' -CountryOrRegion '",  E2,"' -HouseNumber '",  F2, "' -StreetName '",  H2,"' -StreetSuffix '",  I2,"' -City '",  K2,"' -StateOrProvince '",  L2,"' -PostalCode '",  M2,"' -Latitude '",  O2,"' -Longitude '",  P2,"'")</f>
+        <v>New-CsOnlineLisCivicAddress -Description 'OH1' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '100' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'OH' -PostalCode '44314' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R2" s="1" t="str">
+        <f>CONCATENATE("New-CsTeamsEmergencyCallingPolicy -Identity '",A2,"' -ExternalLocationLookupMode Enabled")</f>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity 'OH1' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S2" s="1" t="str">
+        <f>CONCATENATE("New-CsTenantNetworkSite -NetworkRegionID '", E2,"' -NetworkSiteID '",  A2,"' -EmergencyCallingPolicy '",  A2,"'")</f>
+        <v>New-CsTenantNetworkSite -NetworkRegionID 'US' -NetworkSiteID 'OH1' -EmergencyCallingPolicy 'OH1'</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1019,13 +1049,21 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>New-CsOnlineLisCivicAddress -Description 'OH2' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '200' -PreDirectional '' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'OH' -PostalCode '44314' -Latitude '' -Longitude ''</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q3:Q4" si="0">CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A3,"' -CompanyName '",  D3,"' -CountryOrRegion '",  E3,"' -HouseNumber '",  F3, "' -StreetName '",  H3,"' -StreetSuffix '",  I3,"' -City '",  K3,"' -StateOrProvince '",  L3,"' -PostalCode '",  M3,"' -Latitude '",  O3,"' -Longitude '",  P3,"'")</f>
+        <v>New-CsOnlineLisCivicAddress -Description 'OH2' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '200' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'OH' -PostalCode '44314' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R3" s="1" t="str">
+        <f t="shared" ref="R3:R4" si="1">CONCATENATE("New-CsTeamsEmergencyCallingPolicy -Identity '",A3,"' -ExternalLocationLookupMode Enabled")</f>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity 'OH2' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S3" s="1" t="str">
+        <f t="shared" ref="S3:S4" si="2">CONCATENATE("New-CsTenantNetworkSite -NetworkRegionID '", E3,"' -NetworkSiteID '",  A3,"' -EmergencyCallingPolicy '",  A3,"'")</f>
+        <v>New-CsTenantNetworkSite -NetworkRegionID 'US' -NetworkSiteID 'OH2' -EmergencyCallingPolicy 'OH2'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1050,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M4" s="1">
         <v>44314</v>
@@ -1060,13 +1098,1310 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>New-CsOnlineLisCivicAddress -Description 'VA1' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '300' -PreDirectional '' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'VA' -PostalCode '44314' -Latitude '' -Longitude ''</v>
+        <v>New-CsOnlineLisCivicAddress -Description 'VA1' -CompanyName 'CompanyName' -CountryOrRegion 'US' -HouseNumber '300' -StreetName 'Main' -StreetSuffix 'Street' -City 'Akron' -StateOrProvince 'VA' -PostalCode '44314' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity 'VA1' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID 'US' -NetworkSiteID 'VA1' -EmergencyCallingPolicy 'VA1'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q5" t="str">
+        <f t="shared" ref="Q5" si="3">CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A5,"' -CompanyName '",  D5,"' -CountryOrRegion '",  E5,"' -HouseNumber '",  F5, "' -StreetName '",  H5,"' -StreetSuffix '",  I5,"' -City '",  K5,"' -StateOrProvince '",  L5,"' -PostalCode '",  M5,"' -Latitude '",  O5,"' -Longitude '",  P5,"'")</f>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" ref="R5" si="4">CONCATENATE("New-CsTeamsEmergencyCallingPolicy -Identity '",A5,"' -ExternalLocationLookupMode Enabled")</f>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" ref="S5" si="5">CONCATENATE("New-CsTenantNetworkSite -NetworkRegionID '", E5,"' -NetworkSiteID '",  A5,"' -EmergencyCallingPolicy '",  A5,"'")</f>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q6" t="str">
+        <f t="shared" ref="Q6:Q69" si="6">CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A6,"' -CompanyName '",  D6,"' -CountryOrRegion '",  E6,"' -HouseNumber '",  F6, "' -StreetName '",  H6,"' -StreetSuffix '",  I6,"' -City '",  K6,"' -StateOrProvince '",  L6,"' -PostalCode '",  M6,"' -Latitude '",  O6,"' -Longitude '",  P6,"'")</f>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" ref="R6:R69" si="7">CONCATENATE("New-CsTeamsEmergencyCallingPolicy -Identity '",A6,"' -ExternalLocationLookupMode Enabled")</f>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" ref="S6:S69" si="8">CONCATENATE("New-CsTenantNetworkSite -NetworkRegionID '", E6,"' -NetworkSiteID '",  A6,"' -EmergencyCallingPolicy '",  A6,"'")</f>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q7" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q8" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q9" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q10" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q11" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q12" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q13" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q14" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q15" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q16" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="17" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q17" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="18" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q18" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="19" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q19" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R19" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="20" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q20" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="21" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q21" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R21" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="22" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q22" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R22" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="23" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q23" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R23" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="24" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q24" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R24" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S24" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="25" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q25" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R25" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="26" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q26" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R26" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="27" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q27" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R27" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="28" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q28" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R28" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="29" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q29" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R29" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S29" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="30" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q30" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R30" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="31" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q31" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R31" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="32" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q32" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R32" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="33" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q33" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R33" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="34" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q34" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R34" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="35" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q35" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R35" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="36" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q36" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R36" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="37" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q37" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R37" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S37" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="38" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q38" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R38" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S38" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="39" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q39" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R39" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S39" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="40" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q40" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R40" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S40" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="41" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q41" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R41" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S41" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="42" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q42" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R42" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S42" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="43" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q43" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R43" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S43" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="44" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q44" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R44" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S44" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="45" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q45" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R45" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S45" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="46" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q46" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R46" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S46" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="47" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q47" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R47" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S47" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="48" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q48" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R48" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S48" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="49" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q49" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R49" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S49" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="50" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q50" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S50" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="51" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q51" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S51" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="52" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q52" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R52" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S52" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="53" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q53" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R53" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S53" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="54" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q54" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R54" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S54" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="55" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q55" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R55" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S55" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="56" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q56" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R56" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S56" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="57" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q57" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R57" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S57" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="58" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q58" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R58" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S58" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="59" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q59" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R59" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S59" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="60" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q60" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R60" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S60" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="61" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q61" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R61" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S61" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="62" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q62" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R62" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S62" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="63" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q63" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R63" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S63" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="64" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q64" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R64" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S64" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="65" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q65" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R65" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S65" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="66" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q66" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R66" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S66" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="67" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q67" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R67" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S67" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="68" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q68" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R68" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S68" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="69" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q69" t="str">
+        <f t="shared" si="6"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R69" t="str">
+        <f t="shared" si="7"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S69" t="str">
+        <f t="shared" si="8"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="70" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q70" t="str">
+        <f t="shared" ref="Q70:Q96" si="9">CONCATENATE("New-CsOnlineLisCivicAddress -Description '", A70,"' -CompanyName '",  D70,"' -CountryOrRegion '",  E70,"' -HouseNumber '",  F70, "' -StreetName '",  H70,"' -StreetSuffix '",  I70,"' -City '",  K70,"' -StateOrProvince '",  L70,"' -PostalCode '",  M70,"' -Latitude '",  O70,"' -Longitude '",  P70,"'")</f>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R70" t="str">
+        <f t="shared" ref="R70:R96" si="10">CONCATENATE("New-CsTeamsEmergencyCallingPolicy -Identity '",A70,"' -ExternalLocationLookupMode Enabled")</f>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S70" t="str">
+        <f t="shared" ref="S70:S96" si="11">CONCATENATE("New-CsTenantNetworkSite -NetworkRegionID '", E70,"' -NetworkSiteID '",  A70,"' -EmergencyCallingPolicy '",  A70,"'")</f>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="71" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q71" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R71" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S71" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="72" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q72" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R72" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S72" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="73" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q73" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R73" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S73" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="74" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q74" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R74" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S74" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="75" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q75" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R75" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S75" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="76" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q76" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R76" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S76" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="77" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q77" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R77" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S77" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="78" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q78" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R78" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S78" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="79" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q79" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R79" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S79" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="80" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q80" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R80" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S80" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="81" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q81" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R81" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S81" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="82" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q82" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R82" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S82" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="83" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q83" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R83" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S83" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="84" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q84" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R84" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S84" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="85" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q85" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R85" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S85" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="86" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q86" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R86" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S86" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="87" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q87" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R87" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S87" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="88" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q88" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R88" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S88" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="89" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q89" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R89" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S89" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="90" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q90" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R90" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S90" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="91" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q91" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R91" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S91" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="92" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q92" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R92" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S92" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="93" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q93" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R93" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S93" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="94" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q94" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R94" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S94" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="95" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q95" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R95" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S95" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
+      </c>
+    </row>
+    <row r="96" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q96" t="str">
+        <f t="shared" si="9"/>
+        <v>New-CsOnlineLisCivicAddress -Description '' -CompanyName '' -CountryOrRegion '' -HouseNumber '' -StreetName '' -StreetSuffix '' -City '' -StateOrProvince '' -PostalCode '' -Latitude '' -Longitude ''</v>
+      </c>
+      <c r="R96" t="str">
+        <f t="shared" si="10"/>
+        <v>New-CsTeamsEmergencyCallingPolicy -Identity '' -ExternalLocationLookupMode Enabled</v>
+      </c>
+      <c r="S96" t="str">
+        <f t="shared" si="11"/>
+        <v>New-CsTenantNetworkSite -NetworkRegionID '' -NetworkSiteID '' -EmergencyCallingPolicy ''</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1077,10 +2412,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="102.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -1090,32 +2424,32 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
-        <v>43</v>
-      </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="str">
@@ -1123,17 +2457,17 @@
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'FL1'</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="str">
@@ -1141,17 +2475,17 @@
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'FL2'</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="str">
@@ -1159,12 +2493,12 @@
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'Suite100'</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1175,7 +2509,7 @@
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2088,7 +3422,7 @@
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="136.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
   </cols>
@@ -2101,27 +3435,27 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="str">
@@ -2129,18 +3463,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '38-a7-c3-2d-e7-01' -Description 'OH1-FL1-AP1_SSID1_2G' -LocationID ''</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="str">
@@ -2148,18 +3482,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '38-b7-c3-2d-e7-01' -Description 'OH1-FL1-AP1_SSID1_5G' -LocationID ''</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="str">
@@ -2167,18 +3501,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '39-a7-c3-2d-e7-01' -Description 'OH1-FL1-AP1_SSID2_2G' -LocationID ''</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="str">
@@ -2186,18 +3520,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '39-b7-c3-2d-e7-01' -Description 'OH1-FL1-AP1_SSID2_5G' -LocationID ''</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="str">
@@ -2205,18 +3539,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '40-a7-c3-2d-e7-0*' -Description 'OH1-FL2-AP1_2G' -LocationID ''</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="str">
@@ -2224,18 +3558,18 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '40-b7-c3-2d-e7-0*' -Description 'OH1-FL2-AP1_5G' -LocationID ''</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="str">
@@ -2243,7 +3577,7 @@
         <v>Set-CsOnlineLisWirelessAccessPoint -BSSID '41-a1-c3-2d-e7-0*' -Description 'OH1-FL2-AP2' -LocationID ''</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -15649,25 +16983,25 @@
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="39" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="157.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -15675,16 +17009,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="str">
@@ -16302,16 +17636,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
         <v>11</v>
@@ -16322,7 +17656,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -16940,7 +18274,7 @@
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="114" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="109.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -16956,36 +18290,36 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
         <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G1" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="str">
@@ -16993,70 +18327,70 @@
         <v>Set-CsOnlineLisSubnet -Subnet '10.2.1.0' -LocationID '' -Description 'Wireless'</v>
       </c>
       <c r="H2" s="1" t="str">
-        <f>CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A2,"' -MaskBits '",B2,"' -Description '",C2,"' -NetworkSiteID '",E2,"'")</f>
+        <f t="shared" ref="H2:H71" si="0">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A2,"' -MaskBits '",B2,"' -Description '",C2,"' -NetworkSiteID '",E2,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '10.2.1.0' -MaskBits '24' -Description 'Wireless' -NetworkSiteID 'OH1'</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="str">
-        <f t="shared" ref="G3:G71" si="0">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A3,"' -LocationID '",F3,"' -Description '",C3,"'")</f>
+        <f t="shared" ref="G3:G71" si="1">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A3,"' -LocationID '",F3,"' -Description '",C3,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '10.2.2.0' -LocationID '' -Description 'Voice'</v>
       </c>
       <c r="H3" s="1" t="str">
-        <f t="shared" ref="H3:H71" si="1">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A3,"' -MaskBits '",B3,"' -Description '",C3,"' -NetworkSiteID '",E3,"'")</f>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '10.2.2.0' -MaskBits '24' -Description 'Voice' -NetworkSiteID 'OH1'</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1">
         <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '10.133.21.0' -LocationID '' -Description 'Users'</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '10.133.21.0' -MaskBits '24' -Description 'Users' -NetworkSiteID 'OH1'</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F5" s="2"/>
       <c r="G5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17067,7 +18401,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H22" si="3">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A6,"' -MaskBits '",B6,"' -Description '",C6,"' -NetworkSiteID '",E6,"'")</f>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17078,7 +18412,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17088,7 +18422,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17098,7 +18432,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17108,7 +18442,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17118,7 +18452,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17128,7 +18462,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17138,7 +18472,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17148,7 +18482,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17158,7 +18492,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17168,7 +18502,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17179,7 +18513,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17190,7 +18524,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17201,7 +18535,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17211,7 +18545,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17221,7 +18555,7 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -17231,3307 +18565,3307 @@
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="23" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="24" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="25" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="26" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="27" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="28" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="29" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="30" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="31" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H31" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="32" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G38" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="39" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G39" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="40" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G40" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="41" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G41" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="42" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G42" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="43" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G43" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="44" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G44" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="45" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G45" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="46" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G46" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="47" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G47" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H47" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="48" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G48" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H48" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G49" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H50" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G53" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G54" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G56" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G57" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G59" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G60" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G61" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G62" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G64" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G65" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G66" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G67" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G68" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G69" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G70" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G71" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="72" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G72" t="str">
-        <f t="shared" ref="G72:G135" si="4">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A72,"' -LocationID '",F72,"' -Description '",C72,"'")</f>
+        <f t="shared" ref="G72:G135" si="3">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A72,"' -LocationID '",F72,"' -Description '",C72,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H72" t="str">
-        <f t="shared" ref="H72:H135" si="5">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A72,"' -MaskBits '",B72,"' -Description '",C72,"' -NetworkSiteID '",E72,"'")</f>
+        <f t="shared" ref="H72:H135" si="4">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A72,"' -MaskBits '",B72,"' -Description '",C72,"' -NetworkSiteID '",E72,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="73" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G73" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H73" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H73" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="74" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G74" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H74" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H74" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="75" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G75" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H75" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H75" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="76" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G76" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H76" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H76" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="77" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G77" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H77" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H77" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="78" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G78" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H78" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H78" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="79" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G79" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H79" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H79" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="80" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G80" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H80" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H80" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="81" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G81" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H81" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H81" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="82" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G82" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H82" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H82" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="83" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G83" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H83" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H83" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="84" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G84" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H84" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H84" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="85" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G85" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H85" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H85" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="86" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G86" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H86" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H86" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="87" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G87" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H87" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H87" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="88" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G88" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H88" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H88" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="89" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G89" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H89" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H89" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="90" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G90" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H90" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H90" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="91" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G91" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H91" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H91" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="92" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G92" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H92" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H92" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="93" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G93" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H93" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H93" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="94" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G94" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H94" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H94" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="95" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G95" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H95" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H95" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="96" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G96" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H96" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H96" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="97" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G97" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H97" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H97" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="98" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G98" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H98" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H98" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="99" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G99" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H99" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H99" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="100" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G100" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H100" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H100" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="101" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G101" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H101" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H101" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="102" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G102" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H102" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H102" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="103" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G103" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H103" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H103" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="104" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G104" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H104" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H104" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="105" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G105" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H105" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H105" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="106" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G106" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H106" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H106" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="107" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G107" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H107" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H107" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="108" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G108" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H108" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H108" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="109" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G109" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H109" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H109" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="110" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G110" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H110" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H110" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="111" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G111" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H111" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H111" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="112" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G112" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H112" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H112" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="113" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G113" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H113" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H113" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="114" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G114" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H114" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H114" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="115" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G115" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H115" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H115" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="116" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G116" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H116" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H116" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="117" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G117" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H117" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H117" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="118" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G118" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H118" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H118" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="119" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G119" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H119" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H119" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="120" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G120" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H120" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H120" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="121" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G121" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H121" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H121" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="122" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G122" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H122" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H122" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="123" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G123" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H123" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H123" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="124" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G124" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H124" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H124" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="125" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G125" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H125" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H125" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="126" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G126" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H126" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H126" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="127" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G127" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H127" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H127" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="128" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G128" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H128" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H128" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="129" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G129" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H129" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H129" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="130" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G130" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H130" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H130" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="131" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G131" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H131" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H131" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="132" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G132" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H132" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H132" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="133" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G133" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H133" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H133" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="134" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G134" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H134" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H134" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="135" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G135" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H135" t="str">
         <f t="shared" si="4"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H135" t="str">
-        <f t="shared" si="5"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="136" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G136" t="str">
-        <f t="shared" ref="G136:G199" si="6">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A136,"' -LocationID '",F136,"' -Description '",C136,"'")</f>
+        <f t="shared" ref="G136:G199" si="5">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A136,"' -LocationID '",F136,"' -Description '",C136,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H136" t="str">
-        <f t="shared" ref="H136:H199" si="7">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A136,"' -MaskBits '",B136,"' -Description '",C136,"' -NetworkSiteID '",E136,"'")</f>
+        <f t="shared" ref="H136:H199" si="6">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A136,"' -MaskBits '",B136,"' -Description '",C136,"' -NetworkSiteID '",E136,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="137" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G137" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H137" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H137" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="138" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G138" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H138" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H138" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="139" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G139" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H139" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H139" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="140" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G140" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H140" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H140" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="141" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G141" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H141" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H141" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="142" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G142" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H142" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H142" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="143" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G143" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H143" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H143" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="144" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G144" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H144" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H144" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="145" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G145" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H145" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H145" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="146" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G146" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H146" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H146" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="147" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G147" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H147" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H147" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="148" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G148" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H148" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H148" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="149" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G149" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H149" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H149" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="150" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G150" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H150" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H150" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="151" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G151" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H151" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H151" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="152" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G152" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H152" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H152" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="153" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G153" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H153" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H153" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="154" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G154" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H154" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H154" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="155" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G155" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H155" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H155" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="156" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G156" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H156" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H156" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="157" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G157" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H157" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H157" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="158" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G158" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H158" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H158" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="159" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G159" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H159" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H159" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="160" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G160" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H160" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H160" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="161" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G161" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H161" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H161" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="162" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G162" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H162" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H162" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="163" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G163" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H163" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H163" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="164" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G164" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H164" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H164" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="165" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G165" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H165" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H165" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="166" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G166" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H166" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H166" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="167" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G167" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H167" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H167" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="168" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G168" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H168" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H168" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="169" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G169" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H169" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H169" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="170" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G170" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H170" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H170" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="171" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G171" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H171" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H171" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="172" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G172" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H172" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H172" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="173" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G173" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H173" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H173" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="174" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G174" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H174" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H174" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="175" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G175" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H175" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H175" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="176" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G176" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H176" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H176" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="177" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G177" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H177" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H177" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="178" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G178" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H178" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H178" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="179" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G179" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H179" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H179" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="180" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G180" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H180" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H180" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="181" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G181" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H181" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H181" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="182" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G182" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H182" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H182" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="183" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G183" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H183" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H183" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="184" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G184" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H184" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H184" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="185" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G185" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H185" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H185" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="186" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G186" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H186" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H186" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="187" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G187" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H187" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H187" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="188" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G188" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H188" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H188" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="189" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G189" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H189" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H189" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="190" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G190" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H190" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H190" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="191" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G191" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H191" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H191" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="192" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G192" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H192" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H192" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="193" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G193" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H193" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H193" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="194" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G194" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H194" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H194" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="195" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G195" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H195" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H195" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="196" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G196" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H196" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H196" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="197" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G197" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H197" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H197" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="198" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G198" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H198" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H198" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="199" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G199" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H199" t="str">
         <f t="shared" si="6"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H199" t="str">
-        <f t="shared" si="7"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="200" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G200" t="str">
-        <f t="shared" ref="G200:G263" si="8">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A200,"' -LocationID '",F200,"' -Description '",C200,"'")</f>
+        <f t="shared" ref="G200:G263" si="7">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A200,"' -LocationID '",F200,"' -Description '",C200,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H200" t="str">
-        <f t="shared" ref="H200:H263" si="9">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A200,"' -MaskBits '",B200,"' -Description '",C200,"' -NetworkSiteID '",E200,"'")</f>
+        <f t="shared" ref="H200:H263" si="8">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A200,"' -MaskBits '",B200,"' -Description '",C200,"' -NetworkSiteID '",E200,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="201" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G201" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H201" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H201" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="202" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G202" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H202" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H202" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="203" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G203" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H203" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H203" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="204" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G204" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H204" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H204" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="205" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G205" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H205" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H205" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="206" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G206" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H206" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H206" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="207" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G207" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H207" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H207" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="208" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G208" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H208" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H208" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="209" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G209" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H209" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H209" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="210" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G210" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H210" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H210" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="211" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G211" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H211" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H211" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="212" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G212" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H212" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H212" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="213" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G213" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H213" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H213" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="214" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G214" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H214" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H214" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="215" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G215" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H215" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H215" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="216" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G216" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H216" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H216" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="217" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G217" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H217" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H217" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="218" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G218" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H218" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H218" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="219" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G219" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H219" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H219" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="220" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G220" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H220" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H220" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="221" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G221" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H221" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H221" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="222" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G222" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H222" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H222" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="223" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G223" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H223" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H223" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="224" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G224" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H224" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H224" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="225" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G225" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H225" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H225" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="226" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G226" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H226" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H226" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="227" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G227" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H227" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H227" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="228" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G228" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H228" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H228" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="229" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G229" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H229" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H229" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="230" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G230" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H230" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H230" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="231" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G231" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H231" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H231" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="232" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G232" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H232" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H232" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="233" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G233" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H233" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H233" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="234" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G234" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H234" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H234" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="235" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G235" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H235" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H235" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="236" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G236" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H236" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H236" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="237" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G237" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H237" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H237" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="238" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G238" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H238" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H238" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="239" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G239" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H239" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H239" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="240" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G240" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H240" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H240" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="241" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G241" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H241" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H241" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="242" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G242" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H242" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H242" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="243" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G243" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H243" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H243" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="244" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G244" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H244" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H244" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="245" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G245" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H245" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H245" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="246" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G246" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H246" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H246" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="247" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G247" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H247" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H247" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="248" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G248" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H248" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H248" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="249" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G249" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H249" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H249" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="250" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G250" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H250" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H250" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="251" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G251" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H251" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H251" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="252" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G252" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H252" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H252" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="253" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G253" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H253" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H253" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="254" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G254" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H254" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H254" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="255" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G255" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H255" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H255" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="256" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G256" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H256" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H256" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="257" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G257" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H257" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H257" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="258" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G258" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H258" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H258" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="259" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G259" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H259" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H259" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="260" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G260" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H260" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H260" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="261" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G261" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H261" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H261" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="262" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G262" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H262" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H262" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="263" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G263" t="str">
+        <f t="shared" si="7"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H263" t="str">
         <f t="shared" si="8"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H263" t="str">
-        <f t="shared" si="9"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="264" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G264" t="str">
-        <f t="shared" ref="G264:G327" si="10">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A264,"' -LocationID '",F264,"' -Description '",C264,"'")</f>
+        <f t="shared" ref="G264:G327" si="9">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A264,"' -LocationID '",F264,"' -Description '",C264,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H264" t="str">
-        <f t="shared" ref="H264:H327" si="11">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A264,"' -MaskBits '",B264,"' -Description '",C264,"' -NetworkSiteID '",E264,"'")</f>
+        <f t="shared" ref="H264:H327" si="10">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A264,"' -MaskBits '",B264,"' -Description '",C264,"' -NetworkSiteID '",E264,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="265" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G265" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H265" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H265" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="266" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G266" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H266" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H266" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="267" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G267" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H267" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H267" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="268" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G268" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H268" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H268" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="269" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G269" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H269" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H269" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="270" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G270" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H270" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H270" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="271" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G271" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H271" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H271" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="272" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G272" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H272" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H272" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="273" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G273" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H273" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H273" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="274" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G274" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H274" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H274" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="275" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G275" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H275" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H275" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="276" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G276" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H276" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H276" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="277" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G277" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H277" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H277" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="278" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G278" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H278" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H278" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="279" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G279" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H279" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H279" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="280" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G280" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H280" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H280" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="281" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G281" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H281" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H281" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="282" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G282" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H282" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H282" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="283" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G283" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H283" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H283" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="284" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G284" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H284" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H284" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="285" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G285" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H285" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H285" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="286" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G286" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H286" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H286" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="287" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G287" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H287" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H287" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="288" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G288" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H288" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H288" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="289" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G289" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H289" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H289" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="290" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G290" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H290" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H290" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="291" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G291" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H291" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H291" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="292" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G292" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H292" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H292" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="293" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G293" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H293" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H293" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="294" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G294" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H294" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H294" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="295" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G295" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H295" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H295" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="296" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G296" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H296" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H296" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="297" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G297" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H297" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H297" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="298" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G298" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H298" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H298" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="299" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G299" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H299" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H299" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="300" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G300" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H300" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H300" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="301" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G301" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H301" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H301" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="302" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G302" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H302" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H302" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="303" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G303" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H303" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H303" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="304" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G304" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H304" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H304" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="305" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G305" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H305" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H305" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="306" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G306" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H306" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H306" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="307" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G307" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H307" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H307" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="308" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G308" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H308" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H308" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="309" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G309" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H309" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H309" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="310" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G310" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H310" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H310" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="311" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G311" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H311" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H311" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="312" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G312" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H312" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H312" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="313" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G313" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H313" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H313" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="314" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G314" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H314" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H314" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="315" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G315" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H315" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H315" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="316" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G316" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H316" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H316" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="317" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G317" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H317" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H317" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="318" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G318" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H318" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H318" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="319" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G319" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H319" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H319" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="320" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G320" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H320" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H320" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="321" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G321" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H321" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H321" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="322" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G322" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H322" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H322" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="323" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G323" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H323" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H323" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="324" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G324" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H324" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H324" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="325" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G325" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H325" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H325" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="326" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G326" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H326" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H326" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="327" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G327" t="str">
+        <f t="shared" si="9"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H327" t="str">
         <f t="shared" si="10"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H327" t="str">
-        <f t="shared" si="11"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="328" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G328" t="str">
-        <f t="shared" ref="G328:G352" si="12">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A328,"' -LocationID '",F328,"' -Description '",C328,"'")</f>
+        <f t="shared" ref="G328:G352" si="11">CONCATENATE("Set-CsOnlineLisSubnet -Subnet '",A328,"' -LocationID '",F328,"' -Description '",C328,"'")</f>
         <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
       </c>
       <c r="H328" t="str">
-        <f t="shared" ref="H328:H352" si="13">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A328,"' -MaskBits '",B328,"' -Description '",C328,"' -NetworkSiteID '",E328,"'")</f>
+        <f t="shared" ref="H328:H352" si="12">CONCATENATE("New-CsTenantNetworkSubnet -Identity '",A328,"' -MaskBits '",B328,"' -Description '",C328,"' -NetworkSiteID '",E328,"'")</f>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="329" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G329" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H329" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H329" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="330" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G330" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H330" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H330" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="331" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G331" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H331" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H331" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="332" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G332" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H332" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H332" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="333" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G333" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H333" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H333" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="334" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G334" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H334" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H334" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="335" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G335" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H335" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H335" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="336" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G336" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H336" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H336" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="337" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G337" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H337" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H337" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="338" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G338" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H338" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H338" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="339" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G339" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H339" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H339" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="340" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G340" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H340" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H340" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="341" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G341" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H341" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H341" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="342" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G342" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H342" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H342" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="343" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G343" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H343" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H343" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="344" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G344" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H344" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H344" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="345" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G345" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H345" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H345" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="346" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G346" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H346" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H346" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="347" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G347" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H347" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H347" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="348" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G348" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H348" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H348" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="349" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G349" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H349" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H349" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="350" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G350" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H350" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H350" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="351" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G351" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H351" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H351" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
     <row r="352" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G352" t="str">
+        <f t="shared" si="11"/>
+        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
+      </c>
+      <c r="H352" t="str">
         <f t="shared" si="12"/>
-        <v>Set-CsOnlineLisSubnet -Subnet '' -LocationID '' -Description ''</v>
-      </c>
-      <c r="H352" t="str">
-        <f t="shared" si="13"/>
         <v>New-CsTenantNetworkSubnet -Identity '' -MaskBits '' -Description '' -NetworkSiteID ''</v>
       </c>
     </row>
@@ -20578,7 +21912,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>CONCATENATE("New-CsTenantTrustedIPAddress -IPAddress '",A2,"' -MaskBits '",B2,"' -Description '",C2,"'")</f>
@@ -20587,13 +21921,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1">
         <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1" t="str">
         <f>CONCATENATE("New-CsTenantTrustedIPAddress -IPAddress '",A3,"' -MaskBits '",B3,"' -Description '",C3,"'")</f>
@@ -21207,25 +22541,25 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="1"/>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
@@ -21233,7 +22567,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
@@ -21243,22 +22577,22 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1"/>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -21269,10 +22603,10 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -21285,14 +22619,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B23BCF27C13E574080086FDDE9F1AE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0f87443152f07c0e23d3e17cc5e4f2a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xmlns:ns4="7ec81353-5e3c-46ad-b23e-a3059b125bc4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f916432df65b1a2ad2d92eb8b67add4d" ns3:_="" ns4:_="">
     <xsd:import namespace="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
@@ -21531,6 +22857,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -21541,23 +22875,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4EBC72-06B1-4789-81A1-FD517C308153}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7ec81353-5e3c-46ad-b23e-a3059b125bc4"/>
-    <ds:schemaRef ds:uri="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61F3E0B8-93AD-4CE9-93D9-5DE378BA2714}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21576,6 +22893,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4EBC72-06B1-4789-81A1-FD517C308153}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7ec81353-5e3c-46ad-b23e-a3059b125bc4"/>
+    <ds:schemaRef ds:uri="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{672F1083-C076-46D6-BE7D-969F6A47C556}">
   <ds:schemaRefs>

--- a/E911 Workbook.xlsx
+++ b/E911 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30103"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\My Documents\Jobs\C1\C1_Docs\E911\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EAB6BB-E07F-48A5-A197-D54020C351AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFFF441-2DB3-442D-B07E-4FCDBBA6CD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{57AF9C9E-AD33-4CD7-B4AB-20707E2E81EE}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{57AF9C9E-AD33-4CD7-B4AB-20707E2E81EE}"/>
   </bookViews>
   <sheets>
     <sheet name="CivicAddress" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="100">
   <si>
     <t>Description</t>
   </si>
@@ -336,6 +336,12 @@
   <si>
     <t>Network Topology Subnet Add Command</t>
   </si>
+  <si>
+    <t>Import CMD</t>
+  </si>
+  <si>
+    <t>Update Location Name CMD</t>
+  </si>
 </sst>
 </file>
 
@@ -403,12 +409,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -460,16 +467,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3955047C-2C00-494A-ADC5-27AB3BF2E920}" name="Table2" displayName="Table2" ref="A1:F154" totalsRowShown="0" dataCellStyle="Normal">
-  <autoFilter ref="A1:F154" xr:uid="{3955047C-2C00-494A-ADC5-27AB3BF2E920}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3955047C-2C00-494A-ADC5-27AB3BF2E920}" name="Table2" displayName="Table2" ref="A1:G154" totalsRowShown="0" dataCellStyle="Normal">
+  <autoFilter ref="A1:G154" xr:uid="{3955047C-2C00-494A-ADC5-27AB3BF2E920}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{85EF809D-72F3-4C49-82FB-C794DC94B4D7}" name="CivicAddressName" dataCellStyle="Normal"/>
     <tableColumn id="6" xr3:uid="{DAF10671-6023-45B9-8FDA-6363004347B7}" name="CivicAddressID (Leave Blank)"/>
     <tableColumn id="2" xr3:uid="{2CBDFA94-8523-4029-B1FC-EF48C8A05471}" name="CivicAddressLocId (Leave Blank)" dataCellStyle="Normal"/>
     <tableColumn id="3" xr3:uid="{02D4B160-36A1-4756-98EC-A079F7CD1F33}" name="LocationName (Description)" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{312F46C9-DE96-493C-A221-4FADEE17B941}" name="LocationID (Generated in this process)" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{78658000-6A22-4B94-9137-32726F7E3F81}" name="Command" dataCellStyle="Normal">
+    <tableColumn id="4" xr3:uid="{78658000-6A22-4B94-9137-32726F7E3F81}" name="Import CMD" dataCellStyle="Normal">
       <calculatedColumnFormula>CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B2,"' -Location '",D2,"'")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{F76AAE42-3796-4CD5-9801-987F55CA2692}" name="Update Location Name CMD" dataCellStyle="Normal">
+      <calculatedColumnFormula>CONCATENATE("Set-CsOnlineLisLocation -LocationId '",E2,"' -Location '",D2,"'")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2408,7 +2418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3CBB23-FE1F-43BF-98B9-A641B19FF9BA}">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -2416,10 +2426,11 @@
     <col min="4" max="4" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="102.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.85546875" customWidth="1"/>
+    <col min="9" max="9" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -2436,13 +2447,16 @@
         <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
@@ -2456,11 +2470,15 @@
         <f>CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B2,"' -Location '",D2,"'")</f>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'FL1'</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="1" t="str">
+        <f>CONCATENATE("Set-CsOnlineLisLocation -LocationId '",E2,"' -Location '",D2,"'")</f>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location 'FL1'</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -2474,11 +2492,15 @@
         <f t="shared" ref="F3:F66" si="0">CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B3,"' -Location '",D3,"'")</f>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'FL2'</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="1" t="str">
+        <f t="shared" ref="G3:G66" si="1">CONCATENATE("Set-CsOnlineLisLocation -LocationId '",E3,"' -Location '",D3,"'")</f>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location 'FL2'</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -2492,11 +2514,15 @@
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location 'Suite100'</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location 'Suite100'</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -2508,902 +2534,1502 @@
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F6" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F7" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F8" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F9" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F10" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F11" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F12" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F13" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F14" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F16" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F17" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F18" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F19" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F20" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="21" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F21" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F22" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="23" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F23" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="24" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F24" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="25" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F25" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F26" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="27" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F27" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F28" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="29" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F29" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="30" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F30" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="31" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F31" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G31" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="32" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F32" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F33" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F34" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F35" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F36" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F37" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F38" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F39" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F40" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G40" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F41" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F42" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F43" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G43" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F44" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F45" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G45" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F46" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G46" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F47" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G47" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F48" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G48" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G49" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G50" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F51" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F52" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G52" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F53" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G53" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F54" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G54" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F55" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G55" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F56" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G56" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F57" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G57" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F58" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G58" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F59" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G59" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F60" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G60" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F61" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G61" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F62" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G62" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F63" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G63" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F64" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G64" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F65" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G65" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F66" t="str">
         <f t="shared" si="0"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G66" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F67" t="str">
-        <f t="shared" ref="F67:F130" si="1">CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B67,"' -Location '",D67,"'")</f>
+        <f t="shared" ref="F67:F130" si="2">CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B67,"' -Location '",D67,"'")</f>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G67" s="5" t="str">
+        <f t="shared" ref="G67:G130" si="3">CONCATENATE("Set-CsOnlineLisLocation -LocationId '",E67,"' -Location '",D67,"'")</f>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F68" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F69" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F70" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F71" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F72" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F73" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F74" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F75" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F76" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F77" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F78" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F79" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F80" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F81" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F82" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F83" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F84" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F85" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F86" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F87" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F88" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F89" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F90" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F91" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F92" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F93" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F94" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F95" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F96" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F97" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F98" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F99" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F100" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F101" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F102" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F103" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F104" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F105" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F106" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F107" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F108" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F109" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F110" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F111" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F112" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F113" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F114" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F115" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F116" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F117" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F118" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F119" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F120" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F121" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F122" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F123" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F124" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F125" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F126" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="127" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F127" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="128" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F128" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="129" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F129" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="130" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F130" t="str">
-        <f t="shared" si="1"/>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="131" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F131" t="str">
-        <f t="shared" ref="F131:F154" si="2">CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B131,"' -Location '",D131,"'")</f>
-        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
-      </c>
-    </row>
-    <row r="132" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F132" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F133" t="str">
+      <c r="G68" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F69" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F134" t="str">
+      <c r="G69" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F70" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F135" t="str">
+      <c r="G70" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F71" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F136" t="str">
+      <c r="G71" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F72" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F137" t="str">
+      <c r="G72" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F73" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="138" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F138" t="str">
+      <c r="G73" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="139" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F139" t="str">
+      <c r="G74" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="75" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F75" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="140" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F140" t="str">
+      <c r="G75" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="76" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F76" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="141" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F141" t="str">
+      <c r="G76" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="77" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F77" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="142" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F142" t="str">
+      <c r="G77" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="78" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F78" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="143" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F143" t="str">
+      <c r="G78" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="79" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F79" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="144" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F144" t="str">
+      <c r="G79" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="80" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F80" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F145" t="str">
+      <c r="G80" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F81" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F146" t="str">
+      <c r="G81" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F82" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F147" t="str">
+      <c r="G82" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F83" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F148" t="str">
+      <c r="G83" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F84" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F149" t="str">
+      <c r="G84" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F85" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F150" t="str">
+      <c r="G85" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F86" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F151" t="str">
+      <c r="G86" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F87" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F152" t="str">
+      <c r="G87" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F88" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F153" t="str">
+      <c r="G88" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F89" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
       </c>
-    </row>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F154" t="str">
+      <c r="G89" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F90" t="str">
         <f t="shared" si="2"/>
         <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G90" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F91" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G91" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F92" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G92" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="93" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F93" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G93" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="94" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F94" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G94" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="95" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F95" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G95" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="96" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F96" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G96" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="97" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F97" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G97" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="98" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F98" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G98" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="99" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F99" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G99" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="100" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F100" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G100" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="101" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F101" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G101" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="102" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F102" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G102" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="103" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F103" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G103" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="104" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F104" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G104" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="105" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F105" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G105" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="106" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F106" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G106" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="107" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F107" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G107" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="108" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F108" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G108" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="109" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F109" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G109" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="110" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F110" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G110" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="111" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F111" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G111" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="112" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F112" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G112" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F113" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G113" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F114" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G114" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F115" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G115" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F116" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G116" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F117" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G117" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F118" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G118" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F119" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G119" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F120" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G120" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F121" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G121" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="122" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F122" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G122" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="123" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F123" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G123" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="124" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F124" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G124" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="125" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F125" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G125" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="126" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F126" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G126" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="127" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F127" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G127" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="128" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F128" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G128" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="129" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F129" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G129" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="130" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F130" t="str">
+        <f t="shared" si="2"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G130" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="131" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F131" t="str">
+        <f t="shared" ref="F131:F154" si="4">CONCATENATE("New-CsOnlineLisLocation -CivicAddressId '",B131,"' -Location '",D131,"'")</f>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G131" s="5" t="str">
+        <f t="shared" ref="G131:G154" si="5">CONCATENATE("Set-CsOnlineLisLocation -LocationId '",E131,"' -Location '",D131,"'")</f>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="132" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F132" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G132" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="133" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F133" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G133" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="134" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F134" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G134" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="135" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F135" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G135" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="136" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F136" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G136" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="137" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F137" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G137" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="138" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F138" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G138" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="139" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F139" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G139" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="140" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F140" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G140" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="141" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F141" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G141" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="142" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F142" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G142" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="143" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F143" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G143" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="144" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F144" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G144" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="145" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F145" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G145" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="146" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F146" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G146" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="147" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F147" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G147" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="148" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F148" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G148" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="149" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F149" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G149" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="150" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F150" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G150" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="151" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F151" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G151" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="152" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F152" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G152" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="153" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F153" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G153" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
+      </c>
+    </row>
+    <row r="154" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F154" t="str">
+        <f t="shared" si="4"/>
+        <v>New-CsOnlineLisLocation -CivicAddressId '' -Location ''</v>
+      </c>
+      <c r="G154" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Set-CsOnlineLisLocation -LocationId '' -Location ''</v>
       </c>
     </row>
   </sheetData>
@@ -22619,6 +23245,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B23BCF27C13E574080086FDDE9F1AE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0f87443152f07c0e23d3e17cc5e4f2a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xmlns:ns4="7ec81353-5e3c-46ad-b23e-a3059b125bc4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f916432df65b1a2ad2d92eb8b67add4d" ns3:_="" ns4:_="">
     <xsd:import namespace="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
@@ -22857,14 +23491,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -22875,6 +23501,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4EBC72-06B1-4789-81A1-FD517C308153}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7ec81353-5e3c-46ad-b23e-a3059b125bc4"/>
+    <ds:schemaRef ds:uri="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61F3E0B8-93AD-4CE9-93D9-5DE378BA2714}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22893,23 +23536,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4EBC72-06B1-4789-81A1-FD517C308153}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7ec81353-5e3c-46ad-b23e-a3059b125bc4"/>
-    <ds:schemaRef ds:uri="0ed4c8fb-564b-4f70-a3c1-5fe8856c4775"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{672F1083-C076-46D6-BE7D-969F6A47C556}">
   <ds:schemaRefs>
